--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,142 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>120399105</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kramstatjärn, Hls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>559197</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6841476</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järvsö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Många ringformade hackspett på tall</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jens Hansen</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jens Hansen</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120527148</v>
+        <v>120527161</v>
       </c>
       <c r="B2" t="n">
         <v>90580</v>
@@ -773,6 +773,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Gran rötlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -807,11 +807,11 @@
         <v>120399105</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>120399105</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90679</v>
+        <v>90957</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,12 +792,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Frost</t>
+          <t>Bo  Henriksson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,12 +792,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bo  Henriksson</t>
+          <t>Carina Frost</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90963</v>
+        <v>90966</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 41163-2024 artfynd.xlsx
+++ b/artfynd/A 41163-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>120527161</v>
       </c>
       <c r="B2" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
